--- a/data/processed/disputed_ascents.xlsx
+++ b/data/processed/disputed_ascents.xlsx
@@ -1147,13 +1147,13 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9b+</t>
+          <t>9c</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>consensus</t>
+          <t>regraded</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>9b+</t>
+          <t>9c</t>
         </is>
       </c>
       <c r="N11" t="b">
